--- a/artfynd/A 36650-2023 artfynd.xlsx
+++ b/artfynd/A 36650-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123557705</v>
+        <v>123557675</v>
       </c>
       <c r="B2" t="n">
-        <v>78775</v>
+        <v>97350</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>650179</v>
+        <v>650307</v>
       </c>
       <c r="R2" t="n">
-        <v>7163230</v>
+        <v>7163248</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123557711</v>
+        <v>123557669</v>
       </c>
       <c r="B3" t="n">
-        <v>88313</v>
+        <v>57487</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>650288</v>
+        <v>650185</v>
       </c>
       <c r="R3" t="n">
-        <v>7163196</v>
+        <v>7163253</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -853,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Gamla ringhack på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123557767</v>
+        <v>123557703</v>
       </c>
       <c r="B4" t="n">
-        <v>79884</v>
+        <v>78781</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +924,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>650494</v>
+        <v>650320</v>
       </c>
       <c r="R4" t="n">
-        <v>7163129</v>
+        <v>7163182</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -949,12 +954,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123557703</v>
+        <v>123557685</v>
       </c>
       <c r="B5" t="n">
-        <v>78775</v>
+        <v>91001</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>650320</v>
+        <v>650087</v>
       </c>
       <c r="R5" t="n">
-        <v>7163182</v>
+        <v>7163190</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1083,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123557675</v>
+        <v>123557681</v>
       </c>
       <c r="B6" t="n">
-        <v>97333</v>
+        <v>79862</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1100,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>650307</v>
+        <v>650243</v>
       </c>
       <c r="R6" t="n">
-        <v>7163248</v>
+        <v>7163251</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1185,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123557669</v>
+        <v>123557674</v>
       </c>
       <c r="B7" t="n">
-        <v>57481</v>
+        <v>79766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1202,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>650185</v>
+        <v>650057</v>
       </c>
       <c r="R7" t="n">
-        <v>7163253</v>
+        <v>7163251</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1261,11 +1266,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-08-16</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Gamla ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123557681</v>
+        <v>123557676</v>
       </c>
       <c r="B8" t="n">
-        <v>79856</v>
+        <v>97350</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,25 +1304,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>650243</v>
+        <v>650191</v>
       </c>
       <c r="R8" t="n">
-        <v>7163251</v>
+        <v>7163150</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123557674</v>
+        <v>123557705</v>
       </c>
       <c r="B9" t="n">
-        <v>79760</v>
+        <v>78781</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1406,25 +1406,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>650057</v>
+        <v>650179</v>
       </c>
       <c r="R9" t="n">
-        <v>7163251</v>
+        <v>7163230</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123557704</v>
+        <v>123557711</v>
       </c>
       <c r="B10" t="n">
-        <v>78775</v>
+        <v>88330</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,21 +1512,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>650245</v>
+        <v>650288</v>
       </c>
       <c r="R10" t="n">
-        <v>7163226</v>
+        <v>7163196</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1598,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123557676</v>
+        <v>123557767</v>
       </c>
       <c r="B11" t="n">
-        <v>97333</v>
+        <v>79890</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1614,21 +1614,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>6461</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,13 +1638,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>650191</v>
+        <v>650494</v>
       </c>
       <c r="R11" t="n">
-        <v>7163150</v>
+        <v>7163129</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1668,12 +1668,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1700,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123557685</v>
+        <v>123557704</v>
       </c>
       <c r="B12" t="n">
-        <v>90984</v>
+        <v>78781</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1716,21 +1716,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>650087</v>
+        <v>650245</v>
       </c>
       <c r="R12" t="n">
-        <v>7163190</v>
+        <v>7163226</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>

--- a/artfynd/A 36650-2023 artfynd.xlsx
+++ b/artfynd/A 36650-2023 artfynd.xlsx
@@ -1598,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123557767</v>
+        <v>123557704</v>
       </c>
       <c r="B11" t="n">
-        <v>79890</v>
+        <v>78781</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1610,25 +1610,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,13 +1638,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>650494</v>
+        <v>650245</v>
       </c>
       <c r="R11" t="n">
-        <v>7163129</v>
+        <v>7163226</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1668,12 +1668,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1700,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123557704</v>
+        <v>123557767</v>
       </c>
       <c r="B12" t="n">
-        <v>78781</v>
+        <v>79890</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1712,25 +1712,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,13 +1740,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>650245</v>
+        <v>650494</v>
       </c>
       <c r="R12" t="n">
-        <v>7163226</v>
+        <v>7163129</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1770,12 +1770,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 36650-2023 artfynd.xlsx
+++ b/artfynd/A 36650-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123557675</v>
+        <v>123557676</v>
       </c>
       <c r="B2" t="n">
-        <v>97350</v>
+        <v>97367</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>650307</v>
+        <v>650191</v>
       </c>
       <c r="R2" t="n">
-        <v>7163248</v>
+        <v>7163150</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123557669</v>
+        <v>123557767</v>
       </c>
       <c r="B3" t="n">
-        <v>57487</v>
+        <v>79895</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>650185</v>
+        <v>650494</v>
       </c>
       <c r="R3" t="n">
-        <v>7163253</v>
+        <v>7163129</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,17 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Gamla ringhack på gran</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,7 +882,7 @@
         <v>123557703</v>
       </c>
       <c r="B4" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -986,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123557685</v>
+        <v>123557704</v>
       </c>
       <c r="B5" t="n">
-        <v>91001</v>
+        <v>78786</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>650087</v>
+        <v>650245</v>
       </c>
       <c r="R5" t="n">
-        <v>7163190</v>
+        <v>7163226</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1088,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123557681</v>
+        <v>123557675</v>
       </c>
       <c r="B6" t="n">
-        <v>79862</v>
+        <v>97367</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>650243</v>
+        <v>650307</v>
       </c>
       <c r="R6" t="n">
-        <v>7163251</v>
+        <v>7163248</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1190,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123557674</v>
+        <v>123557685</v>
       </c>
       <c r="B7" t="n">
-        <v>79766</v>
+        <v>91006</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6456</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>650057</v>
+        <v>650087</v>
       </c>
       <c r="R7" t="n">
-        <v>7163251</v>
+        <v>7163190</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1292,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123557676</v>
+        <v>123557711</v>
       </c>
       <c r="B8" t="n">
-        <v>97350</v>
+        <v>88335</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>510</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>650191</v>
+        <v>650288</v>
       </c>
       <c r="R8" t="n">
-        <v>7163150</v>
+        <v>7163196</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1397,7 +1392,7 @@
         <v>123557705</v>
       </c>
       <c r="B9" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1496,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123557711</v>
+        <v>123557674</v>
       </c>
       <c r="B10" t="n">
-        <v>88330</v>
+        <v>79771</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1508,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>510</v>
+        <v>6456</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>650288</v>
+        <v>650057</v>
       </c>
       <c r="R10" t="n">
-        <v>7163196</v>
+        <v>7163251</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1598,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123557704</v>
+        <v>123557681</v>
       </c>
       <c r="B11" t="n">
-        <v>78781</v>
+        <v>79867</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1614,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>650245</v>
+        <v>650243</v>
       </c>
       <c r="R11" t="n">
-        <v>7163226</v>
+        <v>7163251</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1700,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123557767</v>
+        <v>123557669</v>
       </c>
       <c r="B12" t="n">
-        <v>79890</v>
+        <v>57490</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1712,25 +1707,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,13 +1735,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>650494</v>
+        <v>650185</v>
       </c>
       <c r="R12" t="n">
-        <v>7163129</v>
+        <v>7163253</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1770,12 +1765,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Gamla ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 36650-2023 artfynd.xlsx
+++ b/artfynd/A 36650-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123557676</v>
+        <v>123557705</v>
       </c>
       <c r="B2" t="n">
-        <v>97367</v>
+        <v>78788</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>650191</v>
+        <v>650179</v>
       </c>
       <c r="R2" t="n">
-        <v>7163150</v>
+        <v>7163230</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123557767</v>
+        <v>123557675</v>
       </c>
       <c r="B3" t="n">
-        <v>79895</v>
+        <v>97369</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6461</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>650494</v>
+        <v>650307</v>
       </c>
       <c r="R3" t="n">
-        <v>7163129</v>
+        <v>7163248</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,12 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123557703</v>
+        <v>123557704</v>
       </c>
       <c r="B4" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>650320</v>
+        <v>650245</v>
       </c>
       <c r="R4" t="n">
-        <v>7163182</v>
+        <v>7163226</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123557704</v>
+        <v>123557676</v>
       </c>
       <c r="B5" t="n">
-        <v>78786</v>
+        <v>97369</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>650245</v>
+        <v>650191</v>
       </c>
       <c r="R5" t="n">
-        <v>7163226</v>
+        <v>7163150</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123557675</v>
+        <v>123557685</v>
       </c>
       <c r="B6" t="n">
-        <v>97367</v>
+        <v>91008</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>650307</v>
+        <v>650087</v>
       </c>
       <c r="R6" t="n">
-        <v>7163248</v>
+        <v>7163190</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123557685</v>
+        <v>123557767</v>
       </c>
       <c r="B7" t="n">
-        <v>91006</v>
+        <v>79897</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6461</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,13 +1225,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>650087</v>
+        <v>650494</v>
       </c>
       <c r="R7" t="n">
-        <v>7163190</v>
+        <v>7163129</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1290,7 +1290,7 @@
         <v>123557711</v>
       </c>
       <c r="B8" t="n">
-        <v>88335</v>
+        <v>88337</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123557705</v>
+        <v>123557681</v>
       </c>
       <c r="B9" t="n">
-        <v>78786</v>
+        <v>79869</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>650179</v>
+        <v>650243</v>
       </c>
       <c r="R9" t="n">
-        <v>7163230</v>
+        <v>7163251</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123557674</v>
+        <v>123557703</v>
       </c>
       <c r="B10" t="n">
-        <v>79771</v>
+        <v>78788</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>650057</v>
+        <v>650320</v>
       </c>
       <c r="R10" t="n">
-        <v>7163251</v>
+        <v>7163182</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123557681</v>
+        <v>123557674</v>
       </c>
       <c r="B11" t="n">
-        <v>79867</v>
+        <v>79773</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,25 +1605,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,7 +1633,7 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>650243</v>
+        <v>650057</v>
       </c>
       <c r="R11" t="n">
         <v>7163251</v>
@@ -1698,7 +1698,7 @@
         <v>123557669</v>
       </c>
       <c r="B12" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 36650-2023 artfynd.xlsx
+++ b/artfynd/A 36650-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123557676</v>
+        <v>123557711</v>
       </c>
       <c r="B2" t="n">
-        <v>96979</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>650191</v>
+        <v>650288</v>
       </c>
       <c r="R2" t="n">
-        <v>7163150</v>
+        <v>7163196</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123557669</v>
+        <v>123557769</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +807,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>650185</v>
+        <v>650476</v>
       </c>
       <c r="R3" t="n">
-        <v>7163253</v>
+        <v>7163111</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,17 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Gamla ringhack på gran</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123557681</v>
+        <v>123557703</v>
       </c>
       <c r="B4" t="n">
-        <v>79891</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>650243</v>
+        <v>650320</v>
       </c>
       <c r="R4" t="n">
-        <v>7163251</v>
+        <v>7163182</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -986,37 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123557711</v>
+        <v>123557704</v>
       </c>
       <c r="B5" t="n">
-        <v>88359</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>650288</v>
+        <v>650245</v>
       </c>
       <c r="R5" t="n">
-        <v>7163196</v>
+        <v>7163226</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1088,19 +1063,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123557704</v>
+        <v>123557705</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1128,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>650245</v>
+        <v>650179</v>
       </c>
       <c r="R6" t="n">
-        <v>7163226</v>
+        <v>7163230</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1190,37 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123557675</v>
+        <v>123557763</v>
       </c>
       <c r="B7" t="n">
-        <v>96979</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,13 +1195,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>650307</v>
+        <v>650633</v>
       </c>
       <c r="R7" t="n">
-        <v>7163248</v>
+        <v>7163114</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1260,12 +1225,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1292,19 +1257,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123557703</v>
+        <v>123557768</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1332,13 +1292,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>650320</v>
+        <v>650475</v>
       </c>
       <c r="R8" t="n">
-        <v>7163182</v>
+        <v>7163094</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1362,12 +1322,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1394,37 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123557705</v>
+        <v>123557674</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>650179</v>
+        <v>650057</v>
       </c>
       <c r="R9" t="n">
-        <v>7163230</v>
+        <v>7163251</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1496,37 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123557767</v>
+        <v>123557681</v>
       </c>
       <c r="B10" t="n">
-        <v>79919</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,13 +1486,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>650494</v>
+        <v>650243</v>
       </c>
       <c r="R10" t="n">
-        <v>7163129</v>
+        <v>7163251</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1566,12 +1516,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1598,37 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123557685</v>
+        <v>123557767</v>
       </c>
       <c r="B11" t="n">
-        <v>91030</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80460</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6461</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,13 +1583,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>650087</v>
+        <v>650494</v>
       </c>
       <c r="R11" t="n">
-        <v>7163190</v>
+        <v>7163129</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1668,12 +1613,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1700,37 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123557674</v>
+        <v>123557669</v>
       </c>
       <c r="B12" t="n">
-        <v>79795</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>650057</v>
+        <v>650185</v>
       </c>
       <c r="R12" t="n">
-        <v>7163251</v>
+        <v>7163253</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1778,6 +1718,11 @@
           <t>2024-08-16</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Gamla ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1799,6 +1744,302 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>123557670</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Fäboliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>650368</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7163226</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Uppflog av 4 hönor</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>123557675</v>
+      </c>
+      <c r="B14" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Fäboliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>650307</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7163248</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>123557676</v>
+      </c>
+      <c r="B15" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Fäboliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>650191</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7163150</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 36650-2023 artfynd.xlsx
+++ b/artfynd/A 36650-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123557711</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123557769</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123557703</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123557704</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123557705</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123557763</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123557768</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123557674</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123557681</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123557767</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1744,6 +1799,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123557669</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1846,6 +1906,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123557670</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1943,6 +2008,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123557675</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2040,8 +2110,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123557676</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>